--- a/sample-data/US-01/sample-po-comprehensive.xlsx
+++ b/sample-data/US-01/sample-po-comprehensive.xlsx
@@ -541,7 +541,7 @@
     <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PURCHASE  ORDER  —  Comprehensive Happy-Path Sample</t>
+          <t>PURCHASE  ORDER</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>PO-2026-FULL-EXCEL-001</t>
+          <t>PO-2026-10012</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Acme Industrial Supplies Ltd</t>
+          <t>Great Lakes Plumbing Supply Co</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ERP-AC-7781</t>
+          <t>ERP-GL-7781</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CRM-ACME-001</t>
+          <t>CRM-GLP-001</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Acme Global Holdings</t>
+          <t>Continental Building Products Group</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Acme North America</t>
+          <t>Continental North America</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Acme Midwest Branch (BR-ACME-MW)</t>
+          <t>Great Lakes Midwest Branch (BR-GLP-MW)</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>john.miller@acme.com</t>
+          <t>john.miller@glps.com</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>PUNCH-AC-001</t>
+          <t>PUNCH-GL-001</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Acme Chicago Warehouse</t>
+          <t>Great Lakes Plumbing - Chicago DC</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CONTRACT-ACME-2026-007</t>
+          <t>CONTRACT-GLP-2026-007</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>ExpressCo (Express) / FastFreight (Ground)</t>
+          <t>PrimeExpress (Express) / Midwest Freight (Ground)</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>SKU-STL-4520</t>
+          <t>SKU-CTG-4520</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Carbon Steel Pipe 4 inch SCH40</t>
+          <t>Ceramic Disc Faucet Cartridge</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="F45" s="8" t="n">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>SKU-FLG-3010</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Stainless Steel Flange 3 inch 150LB</t>
+          <t>Pop-Up Drain Assembly, Brushed Nickel</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Ball Valve 2 inch Full Port CS</t>
+          <t>Pressure-Balancing Shower Valve</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>SKU-PMP-7700</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Centrifugal Pump 5 HP</t>
+          <t>Digital Shower Interface System</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>SKU-GSK-1150</t>
+          <t>SKU-SEL-1150</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Spiral Wound Gasket 3 inch Class 150</t>
+          <t>Tank-to-Bowl Gasket Kit</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Deliver to Dock 3. Forklift required on site. Call warehouse manager 312-555-0199 before arrival. Provide bill of lading + packing list at gate.</t>
+          <t>Deliver to Dock 3. Pallet jack required on site. Call warehouse manager 312-555-0199 before arrival. Provide bill of lading + packing list at gate.</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Blanket order against CONTRACT-ACME-2026-007. Partial shipments allowed. Backorders not required.</t>
+          <t>Blanket order against CONTRACT-GLP-2026-007. Partial shipments allowed. Backorders not required.</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>USA / Germany (per line)</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Standard MTR with shipment</t>
+          <t>Standard compliance certificate with shipment</t>
         </is>
       </c>
     </row>
